--- a/帝国时代2决定版 文明联盟 海战流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 海战流最优研究顺序 By RemonBo.xlsx
@@ -20,9 +20,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·海军本体强化'!$A$1:$E$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·海军本体强化'!$A$1:$E$47</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·海军本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·费用与前置'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·费用与前置'!$A$1:$E$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·费用与前置'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与海战流无关·可跳过'!$A$1:$D$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与海战流无关·可跳过'!$1:$1</definedName>
@@ -1590,7 +1590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>直接强化海军</t>
+          <t>附加火焰伤害</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>直接强化海军</t>
+          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
         </is>
       </c>
     </row>
@@ -1731,14 +1731,14 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1763,9 +1763,9 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1785,14 +1785,14 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>直接强化海军</t>
+          <t>可切换政策风格，按局势临时调整</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1812,14 +1812,14 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>直接强化海军</t>
+          <t>附加范围/冲击伤害，团战更占优</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1844,9 +1844,9 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>直接强化海军</t>
+          <t>研究/生产速度提升，科技与产能来得更快</t>
         </is>
       </c>
     </row>
@@ -1893,11 +1893,11 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>直接强化海军</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>A</t>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>人口容量提升</t>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>直接强化海军</t>
+          <t>解锁升级形态，本流派的上限更高</t>
         </is>
       </c>
     </row>
@@ -2060,9 +2060,9 @@
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -2082,14 +2082,14 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>直接强化海军</t>
+          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -2114,9 +2114,9 @@
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -2141,9 +2141,9 @@
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -2168,9 +2168,9 @@
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2190,14 +2190,14 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>直接强化海军</t>
+          <t>资源存放上限提升，少跑几趟</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -2222,9 +2222,9 @@
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2330,9 +2330,9 @@
       </c>
     </row>
     <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2357,9 +2357,9 @@
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2379,14 +2379,14 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>直接强化海军</t>
+          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
         </is>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2411,9 +2411,9 @@
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2437,7 +2437,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="28" customHeight="1">
+    <row r="32" ht="36" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
           <t>B</t>
@@ -2460,14 +2460,14 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>直接强化海军</t>
+          <t>提升命中率与对移动目标的准确度，减少空枪</t>
         </is>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2492,9 +2492,9 @@
       </c>
     </row>
     <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2514,14 +2514,14 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2541,14 +2541,14 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>直接强化海军</t>
+          <t>资源存放上限提升，少跑几趟</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2568,14 +2568,14 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2595,14 +2595,14 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升</t>
+          <t>额外产出资源，经济滚雪球更快</t>
         </is>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2627,9 +2627,9 @@
       </c>
     </row>
     <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2654,9 +2654,9 @@
       </c>
     </row>
     <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2676,14 +2676,14 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>建造/工作效率提升</t>
+          <t>工作速度提升，成型更快</t>
         </is>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2708,9 +2708,9 @@
       </c>
     </row>
     <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2735,9 +2735,9 @@
       </c>
     </row>
     <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2757,14 +2757,14 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>直接强化海军</t>
+          <t>训练速度提升，成型更快</t>
         </is>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2789,9 +2789,9 @@
       </c>
     </row>
     <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2811,39 +2811,66 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>生命值提升，抗打更久</t>
+          <t>持续回血，长期更省维修成本</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
+          <t>西西里</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>运输船视野 +5 且费用 -50%</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>普鲁人</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>村民/捕鱼船采牡蛎+15%</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>直接强化海军</t>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E46"/>
+  <autoFilter ref="A1:E47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2855,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2996,14 +3023,14 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>资源产出/节省，加快成型</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3023,14 +3050,14 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>直接强化海军</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -3050,14 +3077,14 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>直接强化海军</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3081,35 +3108,8 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>西西里</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>运输船视野 +5 且费用 -50%</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E9"/>
+  <autoFilter ref="A1:E8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>

--- a/帝国时代2决定版 文明联盟 海战流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 海战流最优研究顺序 By RemonBo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开局3免费位" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="后续2000金顺序" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="甲类·海军本体强化" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·费用与前置" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·减费用与资源效率" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="与海战流无关·可跳过" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主选文明推荐" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全62文明总名次" sheetId="7" state="visible" r:id="rId7"/>
@@ -20,10 +20,10 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·海军本体强化'!$A$1:$E$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·海军本体强化'!$A$1:$E$46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·海军本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·费用与前置'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·费用与前置'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与海战流无关·可跳过'!$A$1:$D$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与海战流无关·可跳过'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$16</definedName>
@@ -587,12 +587,12 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>军事建筑/码头建成后食物+55；修船厂/干船坞免费；赤壁战术（爆破船/火焰弓箭手对船只/建筑火焰伤害）</t>
+          <t>军事建筑/码头建成后食物+55；赤壁战术（爆破船/火焰弓箭手对船只/建筑火焰伤害）；卧虎（牵引抛石机/楼船巨型投石武器发更多弹药）</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 3 / 弱 0）；海军科技树 13/19；缺 精锐炮舰、炮舰、德罗蒙战舰、造船匠；最直接一条：军事建筑/码头建成后食物+55</t>
+          <t>阶段1·本体强化；原生条目 7 条（强 3 / 弱 0）；海军科技树 13/19；缺 精锐炮舰、炮舰、德罗蒙战舰、造船匠；最直接一条：军事建筑/码头建成后食物+55</t>
         </is>
       </c>
     </row>
@@ -606,21 +606,21 @@
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 4 条（强 2 / 弱 0）；海军科技树 4/19；缺 大型战舰、快速喷火船、喷火船、喷火船；最直接一条：三列桨手制（单列桨座战船系冲锋造成额外范围伤害且充能更快）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
+          <t>备选：阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；海军科技树 4/19；缺 大型战舰、快速喷火船、喷火船、喷火船；最直接一条：三列桨手制（单列桨座战船系冲锋造成额外范围伤害且充能更快）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="51" customHeight="1">
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼（备选）</t>
+          <t>马来（备选）</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 2 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：渔夫/捕鱼船携带+15</t>
+          <t>备选：阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：海上霸主（码头升级为巨港）</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="4" t="inlineStr"/>
     </row>
-    <row r="6" ht="36" customHeight="1">
+    <row r="6" ht="51" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>第 2 位</t>
@@ -643,12 +643,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>战船封建/城堡/帝王费用-10/15/20%；博格斯维加尔（弓兵系/维京长船攻+1）；码头费用 -15%</t>
+          <t>博格斯维加尔（弓兵系/维京长船攻+1）</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 3 / 弱 0）；海军科技树 11/19；缺 快速喷火船、重型爆破船、精锐炮舰、炮舰；最直接一条：战船封建/城堡/帝王费用-10/15/20%</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；海军科技树 11/19；缺 快速喷火船、重型爆破船、精锐炮舰、炮舰；最直接一条：战船封建/城堡/帝王费用-10/15/20%</t>
         </is>
       </c>
     </row>
@@ -656,27 +656,27 @@
       <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>马来（备选）</t>
+          <t>高丽（备选）</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 3 条（强 2 / 弱 1）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：海上霸主（码头升级为巨港）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
+          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：战船木材-20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="51" customHeight="1">
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>高丽（备选）</t>
+          <t>罗马（备选）</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 2 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：战船木材-20%</t>
+          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 13/19；缺 重型爆破船、精锐炮舰、炮舰、干船坞；最直接一条：箭船系/德罗蒙战舰近战护甲+1/远程护甲+1</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>希腊之火（喷火船射程+1；德罗蒙和炮塔爆炸范围提升）</t>
+          <t>喷火/德罗蒙攻速+25%；希腊之火（喷火船射程+1；德罗蒙和炮塔爆炸范围提升）</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 2 / 弱 0）；海军科技树 15/19；缺 精锐炮舰、炮舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：喷火/德罗蒙攻速+25%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 2 / 弱 0）；海军科技树 15/19；缺 精锐炮舰、炮舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：喷火/德罗蒙攻速+25%</t>
         </is>
       </c>
     </row>
@@ -712,27 +712,27 @@
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>罗马（备选）</t>
+          <t>亚美尼亚（备选）</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 2 / 弱 0）；海军科技树 13/19；缺 重型爆破船、精锐炮舰、炮舰、干船坞；最直接一条：箭船系/德罗蒙战舰近战护甲+1/远程护甲+1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
+          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、造船匠；最直接一条：箭船系/德罗蒙战舰可多发一炮弹</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="51" customHeight="1">
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚（备选）</t>
+          <t>日本（备选）</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 2 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、造船匠；最直接一条：箭船系/德罗蒙战舰可多发一炮弹</t>
+          <t>备选：阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：箭船系视野 +4</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>TC可切换政策风格（经济/海军/军事）；三列桨手制（单列桨座战船系冲锋造成额外范围伤害且充能更快）；提洛同盟（港口/造船厂附近战船攻速+15%）</t>
+          <t>三列桨手制（单列桨座战船系冲锋造成额外范围伤害且充能更快）；提洛同盟（港口/造船厂附近战船攻速+15%）；TC可切换政策风格（经济/海军/军事）</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -823,17 +823,17 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 2 / 弱 0）；海军科技树 4/19；缺 大型战舰、快速喷火船、喷火船、喷火船；最直接一条：三列桨手制（单列桨座战船系冲锋造成额外范围伤害且充能更快）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；海军科技树 4/19；缺 大型战舰、快速喷火船、喷火船、喷火船；最直接一条：三列桨手制（单列桨座战船系冲锋造成额外范围伤害且充能更快）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="51" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>渔夫/捕鱼船携带+15；码头提供的人口空间 +5</t>
+          <t>海上霸主（码头升级为巨港）；码头视野 +6；养鱼场费用-33%且食物+200%</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：渔夫/捕鱼船携带+15</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：海上霸主（码头升级为巨港）</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>海上霸主（码头升级为巨港）；码头视野 +6</t>
+          <t>战船木材-20%；神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -883,17 +883,17 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：海上霸主（码头升级为巨港）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：战船木材-20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="51" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>战船木材-20%；神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）</t>
+          <t>箭船系/德罗蒙战舰近战护甲+1/远程护甲+1；弩炮（蝎式弩攻速+33%；箭船系攻+2）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -913,17 +913,17 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：战船木材-20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 13/19；缺 重型爆破船、精锐炮舰、炮舰、干船坞；最直接一条：箭船系/德罗蒙战舰近战护甲+1/远程护甲+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="51" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>箭船系/德罗蒙战舰近战护甲+1/远程护甲+1；弩炮（蝎式弩攻速+33%；箭船系攻+2）</t>
+          <t>箭船系/德罗蒙战舰可多发一炮弹；奇里乞亚舰队（爆破船爆炸范围+20%；箭船系/德罗蒙战舰射程+1）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -943,17 +943,17 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；海军科技树 13/19；缺 重型爆破船、精锐炮舰、炮舰、干船坞；最直接一条：箭船系/德罗蒙战舰近战护甲+1/远程护甲+1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、造船匠；最直接一条：箭船系/德罗蒙战舰可多发一炮弹</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="51" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -963,27 +963,27 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>箭船系/德罗蒙战舰可多发一炮弹；奇里乞亚舰队（爆破船爆炸范围+20%；箭船系/德罗蒙战舰射程+1）</t>
+          <t>箭船系视野 +4；捕鱼船黑暗/封建/城堡/帝王工作+5/10/15/20%，生命+100%</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>黑暗时代起</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、造船匠；最直接一条：箭船系/德罗蒙战舰可多发一炮弹</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：箭船系视野 +4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="51" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -993,27 +993,27 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>捕鱼船黑暗/封建/城堡/帝王工作+5/10/15/20%，生命+100%；箭船系视野 +4</t>
+          <t>码头/大学科技-25%；捕鱼船-15%</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>黑暗时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：箭船系视野 +4</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：码头/大学科技-25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="51" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>码头/大学科技-25%；捕鱼船-15%</t>
+          <t>瓦兰吉/维京长船移速+10%；北方人之怒（投石车系/大型投石战舰射程+1；攻城武器/攻城战舰对建筑攻+40%）</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：码头/大学科技-25%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 0）；海军科技树 13/19；缺 重型爆破船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：瓦兰吉/维京长船移速+10%</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>捕鱼船/村民存食+5%；瓦兰吉/维京长船移速+10%；北方人之怒（投石车系/大型投石战舰射程+1；攻城武器/攻城战舰对建筑攻+40%）</t>
+          <t>维京长船/大型投石战舰攻速+15%；牧羊/捕鱼/狩猎也产黄金</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1 / 弱 0）；海军科技树 13/19；缺 重型爆破船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：瓦兰吉/维京长船移速+10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；海军科技树 13/19；缺 重型爆破船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：维京长船/大型投石战舰攻速+15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="51" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>维京长船/大型投石战舰攻速+15%</t>
+          <t>火炮术（炮塔/手推炮/炮舰射程+2）</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；海军科技树 13/19；缺 重型爆破船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：维京长船/大型投石战舰攻速+15%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；海军科技树 15/19；缺 快速喷火船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：火炮术（炮塔/手推炮/炮舰射程+2）</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>火炮术（炮塔/手推炮/炮舰射程+2）</t>
+          <t>弩箭匣（弓兵系/战车/楼船可发更多弩箭）；攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；海军科技树 15/19；缺 快速喷火船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：火炮术（炮塔/手推炮/炮舰射程+2）</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1143,17 +1143,17 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>TC/码头生命+100%，黑暗/封建/城堡/帝王工作速度+5/10/15/20%</t>
+          <t>箭船系攻速+25%；运输船生命+100%，运载+20</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>黑暗时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；海军科技树 15/19；缺 德罗蒙战舰、造船匠、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：TC/码头生命+100%，黑暗/封建/城堡/帝王工作速度+5/10/15/20%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 14/19；缺 快速喷火船、德罗蒙战舰、造船匠、精锐卡拉维尔战舰；最直接一条：箭船系攻速+25%</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1173,27 +1173,27 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>攻城武器/攻城战舰城堡/帝王移速+10/15%；弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
+          <t>炮舰攻击移动目标更准</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：炮舰攻击移动目标更准</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="51" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1203,27 +1203,27 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>箭船系攻速+25%；运输船生命+100%，运载+20</t>
+          <t>火矛兵/喷火船城堡/帝王移速+5/10%；火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；海军科技树 14/19；缺 快速喷火船、德罗蒙战舰、造船匠、精锐卡拉维尔战舰；最直接一条：箭船系攻速+25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：火矛兵/喷火船城堡/帝王移速+5/10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="51" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>炮舰攻击移动目标更准</t>
+          <t>希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）；伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1243,17 +1243,17 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：炮舰攻击移动目标更准</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 0）；海军科技树 3/19；缺 大型战舰、快速喷火船、喷火船、喷火船；最直接一条：希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="51" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -1263,27 +1263,27 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>火矛兵/喷火船城堡/帝王移速+5/10%；火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
+          <t>维京长船/大型投石战舰生命+20%</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：火矛兵/喷火船城堡/帝王移速+5/10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="66" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；海军科技树 12/19；缺 快速喷火船、重型爆破船、精锐炮舰、炮舰；最直接一条：维京长船/大型投石战舰生命+20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="51" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>村民/捕鱼船存食+10%；希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）；伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
+          <t>霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 0）；海军科技树 3/19；缺 大型战舰、快速喷火船、喷火船、喷火船；最直接一条：希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；海军科技树 11/19；缺 快速喷火船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="51" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>维京长船/大型投石战舰生命+20%</t>
+          <t>芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1333,17 +1333,17 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；海军科技树 12/19；缺 快速喷火船、重型爆破船、精锐炮舰、炮舰；最直接一条：维京长船/大型投石战舰生命+20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 4/19；缺 大型战舰、快速喷火船、喷火船、喷火船；最直接一条：芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1353,17 +1353,17 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
+          <t>船舰封建/城堡/帝王生命+10/15/20%；环球探险（地图全待探索；船只训练+33%）</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>封建时代起</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；海军科技树 11/19；缺 快速喷火船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 1）；海军科技树 15/19；缺 快速喷火船、重型爆破船、德罗蒙战舰、造船匠</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>牵引抛石机/楼船费用-25%</t>
+          <t>船舰移速+10%</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；海军科技树 11/19；缺 重型爆破船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：牵引抛石机/楼船费用-25%</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>造船厂工作速度+15%；芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
+          <t>船舰每分钟回15生命</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；海军科技树 4/19；缺 大型战舰、快速喷火船、喷火船、喷火船；最直接一条：芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="51" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1443,17 +1443,17 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>船舰封建/城堡/帝王生命+10/15/20%；环球探险（地图全待探索；船只训练+33%）</t>
+          <t>牵引抛石机/楼船费用-25%</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>封建时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 0）；海军科技树 15/19；缺 快速喷火船、重型爆破船、德罗蒙战舰、造船匠</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；海军科技树 11/19；缺 重型爆破船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：牵引抛石机/楼船费用-25%</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>船舰移速+10%</t>
+          <t>运输船视野 +5 且费用 -50%</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1483,17 +1483,17 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="36" customHeight="1">
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；海军科技树 15/19；缺 精锐炮舰、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="51" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>船舰每分钟回15生命</t>
+          <t>渔夫/捕鱼船携带+15；码头提供的人口空间 +5</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="36" customHeight="1">
+          <t>阶段3·资源效率；原生条目 4 条（强 2 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：渔夫/捕鱼船携带+15</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="51" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1533,17 +1533,17 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>运输船视野 +5 且费用 -50%</t>
+          <t>TC/码头生命+100%，黑暗/封建/城堡/帝王工作速度+5/10/15/20%</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>黑暗时代起</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；海军科技树 15/19；缺 精锐炮舰、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
+          <t>阶段3·资源效率；原生条目 2 条（强 1 / 弱 0）；海军科技树 15/19；缺 德罗蒙战舰、造船匠、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：TC/码头生命+100%，黑暗/封建/城堡/帝王工作速度+5/10/15/20%</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；海军科技树 3/19；缺 大型战舰、快速喷火船、喷火船、喷火船</t>
+          <t>阶段3·资源效率；原生条目 1 条（强 0 / 弱 0）；海军科技树 3/19；缺 大型战舰、快速喷火船、喷火船、喷火船</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1716,22 +1716,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>博格斯维加尔（弓兵系/维京长船攻+1）</t>
+          <t>修船厂/干船坞免费</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>免费获得，等于直接省下这笔支出</t>
         </is>
       </c>
     </row>
@@ -1743,76 +1743,76 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>维京</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>博格斯维加尔（弓兵系/维京长船攻+1）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>拜占庭</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>喷火/德罗蒙攻速+25%</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>攻速提升，直接抬高输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>拜占庭</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>希腊之火（喷火船射程+1；德罗蒙和炮塔爆炸范围提升）</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>爆炸/溅射范围提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>TC可切换政策风格（经济/海军/军事）</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>可切换政策风格，按局势临时调整</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>三列桨手制（单列桨座战船系冲锋造成额外范围伤害且充能更快）</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>附加范围/冲击伤害，团战更占优</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>提洛同盟（港口/造船厂附近战船攻速+15%）</t>
+          <t>三列桨手制（单列桨座战船系冲锋造成额外范围伤害且充能更快）</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>攻速提升，直接抬高输出</t>
+          <t>附加范围/冲击伤害，团战更占优</t>
         </is>
       </c>
     </row>
@@ -1856,17 +1856,17 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>造船厂科技研究速度 +50%</t>
+          <t>提洛同盟（港口/造船厂附近战船攻速+15%）</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>研究/生产速度提升，科技与产能来得更快</t>
+          <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>渔夫/捕鱼船携带+15</t>
+          <t>TC可切换政策风格（经济/海军/军事）</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1893,11 +1893,11 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
+          <t>可切换政策风格，按局势临时调整</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>A</t>
@@ -1905,12 +1905,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>码头提供的人口空间 +5</t>
+          <t>造船厂科技研究速度 +50%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
+          <t>研究/生产速度提升，科技与产能来得更快</t>
         </is>
       </c>
     </row>
@@ -1986,22 +1986,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）</t>
+          <t>养鱼场费用-33%且食物+200%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>射程提升</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
@@ -2013,12 +2013,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>箭船系/德罗蒙战舰近战护甲+1/远程护甲+1</t>
+          <t>战船木材-20%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
@@ -2040,130 +2040,130 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>高丽</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>射程提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>罗马</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>箭船系/德罗蒙战舰近战护甲+1/远程护甲+1</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>罗马</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>弩炮（蝎式弩攻速+33%；箭船系攻+2）</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>亚美尼亚</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>箭船系/德罗蒙战舰可多发一炮弹</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>额外一次的投掷/发射，等于直接翻倍输出</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>亚美尼亚</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>奇里乞亚舰队（爆破船爆炸范围+20%；箭船系/德罗蒙战舰射程+1）</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>爆炸/溅射范围提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>日本</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>捕鱼船黑暗/封建/城堡/帝王工作+5/10/15/20%，生命+100%</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>日本</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>箭船系视野 +4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>视野提升</t>
         </is>
       </c>
     </row>
@@ -2175,22 +2175,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>捕鱼船/村民存食+5%</t>
+          <t>箭船系视野 +4</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>资源存放上限提升，少跑几趟</t>
+          <t>视野提升</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>瓦兰吉/维京长船移速+10%</t>
+          <t>捕鱼船黑暗/封建/城堡/帝王工作+5/10/15/20%，生命+100%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2217,11 +2217,11 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>机动性提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="36" customHeight="1">
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
           <t>B</t>
@@ -2229,22 +2229,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>北方人之怒（投石车系/大型投石战舰射程+1；攻城武器/攻城战舰对建筑攻+40%）</t>
+          <t>码头/大学科技-25%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>射程提升</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
@@ -2256,12 +2256,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>维京长船/大型投石战舰攻速+15%</t>
+          <t>捕鱼船-15%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>攻速提升，直接抬高输出</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
@@ -2283,49 +2283,49 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>火炮术（炮塔/手推炮/炮舰射程+2）</t>
+          <t>瓦兰吉/维京长船移速+10%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>机动性提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>北方人之怒（投石车系/大型投石战舰射程+1；攻城武器/攻城战舰对建筑攻+40%）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>射程提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>波斯</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>TC/码头生命+100%，黑暗/封建/城堡/帝王工作速度+5/10/15/20%</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
@@ -2337,12 +2337,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
+          <t>维京长船/大型投石战舰攻速+15%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>机动性提升</t>
+          <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
@@ -2364,22 +2364,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
+          <t>牧羊/捕鱼/狩猎也产黄金</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
+          <t>采集效率提升，经济成型更快</t>
         </is>
       </c>
     </row>
@@ -2391,22 +2391,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>箭船系攻速+25%</t>
+          <t>火炮术（炮塔/手推炮/炮舰射程+2）</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>攻速提升，直接抬高输出</t>
+          <t>射程提升</t>
         </is>
       </c>
     </row>
@@ -2418,238 +2418,238 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
+          <t>蜀</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>蜀</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>机动性提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>萨拉森</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>箭船系攻速+25%</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>攻速提升，直接抬高输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>萨拉森</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>运输船生命+100%，运载+20</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>西班牙</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>炮舰攻击移动目标更准</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>提升命中率与对移动目标的准确度，减少空枪</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>中国</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>火矛兵/喷火船城堡/帝王移速+5/10%</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>机动性提升</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>中国</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>斯巴达</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>村民/捕鱼船存食+10%</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>资源存放上限提升，少跑几趟</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="36" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>斯巴达</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升，正面更硬</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>额外产出资源，经济滚雪球更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>撒克逊人</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>维京长船/大型投石战舰生命+20%</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>女真</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>爆炸/溅射范围提升</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>造船厂工作速度+15%</t>
+          <t>维京长船/大型投石战舰生命+20%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>工作速度提升，成型更快</t>
+          <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
@@ -2688,12 +2688,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
+          <t>霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>攻速提升，直接抬高输出</t>
+          <t>爆炸/溅射范围提升</t>
         </is>
       </c>
     </row>
@@ -2715,22 +2715,22 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>船舰封建/城堡/帝王生命+10/15/20%</t>
+          <t>芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>生命值提升，抗打更久</t>
+          <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
@@ -2747,17 +2747,17 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>环球探险（地图全待探索；船只训练+33%）</t>
+          <t>船舰封建/城堡/帝王生命+10/15/20%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>训练速度提升，成型更快</t>
+          <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
@@ -2769,22 +2769,22 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>船舰移速+10%</t>
+          <t>环球探险（地图全待探索；船只训练+33%）</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>机动性提升</t>
+          <t>训练速度提升，成型更快</t>
         </is>
       </c>
     </row>
@@ -2796,12 +2796,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>船舰每分钟回15生命</t>
+          <t>船舰移速+10%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>持续回血，长期更省维修成本</t>
+          <t>机动性提升</t>
         </is>
       </c>
     </row>
@@ -2823,54 +2823,27 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>运输船视野 +5 且费用 -50%</t>
+          <t>船舰每分钟回15生命</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>普鲁人</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>村民/捕鱼船采牡蛎+15%</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
+          <t>持续回血，长期更省维修成本</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E47"/>
+  <autoFilter ref="A1:E46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2882,7 +2855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2927,12 +2900,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>修船厂/干船坞免费</t>
+          <t>战船封建/城堡/帝王费用-10/15/20%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2942,7 +2915,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>免费获得，等于直接省下这笔支出</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
@@ -2959,61 +2932,61 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>战船封建/城堡/帝王费用-10/15/20%</t>
+          <t>码头费用 -15%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>捕鱼船/村民存食+5%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>维京</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>码头费用 -15%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>资源存放上限提升，少跑几趟</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>战船木材-20%</t>
+          <t>村民/捕鱼船存食+10%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -3023,24 +2996,24 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>资源存放上限提升，少跑几趟</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>码头/大学科技-25%</t>
+          <t>造船厂工作速度+15%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -3050,24 +3023,24 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>工作速度提升，成型更快</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>捕鱼船-15%</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -3108,8 +3081,143 @@
         </is>
       </c>
     </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>西西里</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>运输船视野 +5 且费用 -50%</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>达罗毗荼</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>渔夫/捕鱼船携带+15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>达罗毗荼</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>码头提供的人口空间 +5</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>波斯</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>TC/码头生命+100%，黑暗/封建/城堡/帝王工作速度+5/10/15/20%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>普鲁人</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>村民/捕鱼船采牡蛎+15%</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E8"/>
+  <autoFilter ref="A1:E13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -4034,22 +4142,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>15/19</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>渔夫/捕鱼船携带+15；码头提供的人口空间 +5</t>
+          <t>海上霸主（码头升级为巨港）；码头视野 +6</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；海军科技树 16/19。缺：德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
+          <t>原生条目 3 条（强 2）；海军科技树 15/19。缺：重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4167,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -4069,12 +4177,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>海上霸主（码头升级为巨港）；码头视野 +6</t>
+          <t>战船木材-20%；神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2）；海军科技树 15/19。缺：重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
+          <t>原生条目 2 条（强 2）；海军科技树 15/19。缺：重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
         </is>
       </c>
     </row>
@@ -4084,22 +4192,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>13/19</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>战船木材-20%；神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）</t>
+          <t>箭船系/德罗蒙战舰近战护甲+1/远程护甲+1；弩炮（蝎式弩攻速+33%；箭船系攻+2）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；海军科技树 15/19。缺：重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
+          <t>原生条目 2 条（强 2）；海军科技树 13/19。缺：重型爆破船、精锐炮舰、炮舰、干船坞、精锐卡拉维尔战舰</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4217,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -4119,12 +4227,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>箭船系/德罗蒙战舰近战护甲+1/远程护甲+1；弩炮（蝎式弩攻速+33%；箭船系攻+2）</t>
+          <t>箭船系/德罗蒙战舰可多发一炮弹；奇里乞亚舰队（爆破船爆炸范围+20%；箭船系/德罗蒙战舰射程+1）</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；海军科技树 13/19。缺：重型爆破船、精锐炮舰、炮舰、干船坞、精锐卡拉维尔战舰</t>
+          <t>原生条目 2 条（强 2）；海军科技树 13/19。缺：快速喷火船、精锐炮舰、炮舰、造船匠、精锐卡拉维尔战舰</t>
         </is>
       </c>
     </row>
@@ -4134,22 +4242,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>15/19</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>箭船系/德罗蒙战舰可多发一炮弹；奇里乞亚舰队（爆破船爆炸范围+20%；箭船系/德罗蒙战舰射程+1）</t>
+          <t>箭船系视野 +4</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；海军科技树 13/19。缺：快速喷火船、精锐炮舰、炮舰、造船匠、精锐卡拉维尔战舰</t>
+          <t>原生条目 2 条（强 1）；海军科技树 15/19。缺：重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4267,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -4169,7 +4277,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>箭船系视野 +4</t>
+          <t>码头/大学科技-25%</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -4184,22 +4292,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>13/19</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>码头/大学科技-25%</t>
+          <t>瓦兰吉/维京长船移速+10%</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1）；海军科技树 15/19。缺：重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
+          <t>原生条目 3 条（强 1）；海军科技树 13/19。缺：重型爆破船、精锐炮舰、炮舰、德罗蒙战舰、精锐卡拉维尔战舰</t>
         </is>
       </c>
     </row>
@@ -4209,7 +4317,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -4219,12 +4327,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>瓦兰吉/维京长船移速+10%</t>
+          <t>维京长船/大型投石战舰攻速+15%</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1）；海军科技树 13/19。缺：重型爆破船、精锐炮舰、炮舰、德罗蒙战舰、精锐卡拉维尔战舰</t>
+          <t>原生条目 2 条（强 1）；海军科技树 13/19。缺：重型爆破船、精锐炮舰、炮舰、德罗蒙战舰、精锐卡拉维尔战舰</t>
         </is>
       </c>
     </row>
@@ -4234,22 +4342,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>15/19</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>维京长船/大型投石战舰攻速+15%</t>
+          <t>火炮术（炮塔/手推炮/炮舰射程+2）</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1）；海军科技树 13/19。缺：重型爆破船、精锐炮舰、炮舰、德罗蒙战舰、精锐卡拉维尔战舰</t>
+          <t>原生条目 1 条（强 1）；海军科技树 15/19。缺：快速喷火船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
         </is>
       </c>
     </row>
@@ -4259,22 +4367,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>13/19</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>火炮术（炮塔/手推炮/炮舰射程+2）</t>
+          <t>弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；海军科技树 15/19。缺：快速喷火船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
+          <t>原生条目 2 条（强 1）；海军科技树 13/19。缺：快速喷火船、精锐炮舰、炮舰、德罗蒙战舰、精锐卡拉维尔战舰</t>
         </is>
       </c>
     </row>
@@ -4284,22 +4392,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>14/19</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>TC/码头生命+100%，黑暗/封建/城堡/帝王工作速度+5/10/15/20%</t>
+          <t>箭船系攻速+25%</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；海军科技树 15/19。缺：德罗蒙战舰、造船匠、精锐卡拉维尔战舰、卡拉维尔战舰</t>
+          <t>原生条目 2 条（强 1）；海军科技树 14/19。缺：快速喷火船、德罗蒙战舰、造船匠、精锐卡拉维尔战舰、卡拉维尔战舰</t>
         </is>
       </c>
     </row>
@@ -4380,16 +4488,16 @@
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>军事建筑/码头建成后食物+55；修船厂/干船坞免费；赤壁战术（爆破船/火焰弓箭手对船只/建筑火焰伤害）</t>
+          <t>军事建筑/码头建成后食物+55；赤壁战术（爆破船/火焰弓箭手对船只/建筑火焰伤害）；卧虎（牵引抛石机/楼船巨型投石武器发更多弹药）</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 3 / 弱 0）；海军科技树 13/19；缺 精锐炮舰、炮舰、德罗蒙战舰、造船匠；最直接一条：军事建筑/码头建成后食物+55</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 7 条（强 3 / 弱 0）；海军科技树 13/19；缺 精锐炮舰、炮舰、德罗蒙战舰、造船匠；最直接一条：军事建筑/码头建成后食物+55</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="51" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -4410,16 +4518,16 @@
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>战船封建/城堡/帝王费用-10/15/20%；博格斯维加尔（弓兵系/维京长船攻+1）；码头费用 -15%</t>
+          <t>博格斯维加尔（弓兵系/维京长船攻+1）</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 3 / 弱 0）；海军科技树 11/19；缺 快速喷火船、重型爆破船、精锐炮舰、炮舰；最直接一条：战船封建/城堡/帝王费用-10/15/20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；海军科技树 11/19；缺 快速喷火船、重型爆破船、精锐炮舰、炮舰；最直接一条：战船封建/城堡/帝王费用-10/15/20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="51" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -4440,12 +4548,12 @@
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>希腊之火（喷火船射程+1；德罗蒙和炮塔爆炸范围提升）</t>
+          <t>喷火/德罗蒙攻速+25%；希腊之火（喷火船射程+1；德罗蒙和炮塔爆炸范围提升）</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 2 / 弱 0）；海军科技树 15/19；缺 精锐炮舰、炮舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：喷火/德罗蒙攻速+25%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 2 / 弱 0）；海军科技树 15/19；缺 精锐炮舰、炮舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：喷火/德罗蒙攻速+25%</t>
         </is>
       </c>
     </row>
@@ -4470,22 +4578,22 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>TC可切换政策风格（经济/海军/军事）；三列桨手制（单列桨座战船系冲锋造成额外范围伤害且充能更快）；提洛同盟（港口/造船厂附近战船攻速+15%）</t>
+          <t>三列桨手制（单列桨座战船系冲锋造成额外范围伤害且充能更快）；提洛同盟（港口/造船厂附近战船攻速+15%）；TC可切换政策风格（经济/海军/军事）</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 2 / 弱 0）；海军科技树 4/19；缺 大型战舰、快速喷火船、喷火船、喷火船；最直接一条：三列桨手制（单列桨座战船系冲锋造成额外范围伤害且充能更快）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；海军科技树 4/19；缺 大型战舰、快速喷火船、喷火船、喷火船；最直接一条：三列桨手制（单列桨座战船系冲锋造成额外范围伤害且充能更快）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="51" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -4500,12 +4608,12 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>渔夫/捕鱼船携带+15；码头提供的人口空间 +5</t>
+          <t>海上霸主（码头升级为巨港）；码头视野 +6；养鱼场费用-33%且食物+200%</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：渔夫/捕鱼船携带+15</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：海上霸主（码头升级为巨港）</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4623,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -4530,22 +4638,22 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>海上霸主（码头升级为巨港）；码头视野 +6</t>
+          <t>战船木材-20%；神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：海上霸主（码头升级为巨港）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：战船木材-20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="51" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -4560,22 +4668,22 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>战船木材-20%；神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）</t>
+          <t>箭船系/德罗蒙战舰近战护甲+1/远程护甲+1；弩炮（蝎式弩攻速+33%；箭船系攻+2）</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：战船木材-20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 13/19；缺 重型爆破船、精锐炮舰、炮舰、干船坞；最直接一条：箭船系/德罗蒙战舰近战护甲+1/远程护甲+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="51" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4590,22 +4698,22 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>箭船系/德罗蒙战舰近战护甲+1/远程护甲+1；弩炮（蝎式弩攻速+33%；箭船系攻+2）</t>
+          <t>箭船系/德罗蒙战舰可多发一炮弹；奇里乞亚舰队（爆破船爆炸范围+20%；箭船系/德罗蒙战舰射程+1）</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；海军科技树 13/19；缺 重型爆破船、精锐炮舰、炮舰、干船坞；最直接一条：箭船系/德罗蒙战舰近战护甲+1/远程护甲+1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、造船匠；最直接一条：箭船系/德罗蒙战舰可多发一炮弹</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="51" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -4620,22 +4728,22 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>箭船系/德罗蒙战舰可多发一炮弹；奇里乞亚舰队（爆破船爆炸范围+20%；箭船系/德罗蒙战舰射程+1）</t>
+          <t>箭船系视野 +4；捕鱼船黑暗/封建/城堡/帝王工作+5/10/15/20%，生命+100%</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、造船匠；最直接一条：箭船系/德罗蒙战舰可多发一炮弹</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：箭船系视野 +4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="51" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -4650,22 +4758,22 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>捕鱼船黑暗/封建/城堡/帝王工作+5/10/15/20%，生命+100%；箭船系视野 +4</t>
+          <t>码头/大学科技-25%；捕鱼船-15%</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：箭船系视野 +4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：码头/大学科技-25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="51" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -4680,12 +4788,12 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>码头/大学科技-25%；捕鱼船-15%</t>
+          <t>瓦兰吉/维京长船移速+10%；北方人之怒（投石车系/大型投石战舰射程+1；攻城武器/攻城战舰对建筑攻+40%）</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：码头/大学科技-25%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 0）；海军科技树 13/19；缺 重型爆破船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：瓦兰吉/维京长船移速+10%</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4803,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -4710,22 +4818,22 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>捕鱼船/村民存食+5%；瓦兰吉/维京长船移速+10%；北方人之怒（投石车系/大型投石战舰射程+1；攻城武器/攻城战舰对建筑攻+40%）</t>
+          <t>维京长船/大型投石战舰攻速+15%；牧羊/捕鱼/狩猎也产黄金</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1 / 弱 0）；海军科技树 13/19；缺 重型爆破船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：瓦兰吉/维京长船移速+10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；海军科技树 13/19；缺 重型爆破船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：维京长船/大型投石战舰攻速+15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="51" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -4740,12 +4848,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>维京长船/大型投石战舰攻速+15%</t>
+          <t>火炮术（炮塔/手推炮/炮舰射程+2）</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；海军科技树 13/19；缺 重型爆破船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：维京长船/大型投石战舰攻速+15%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；海军科技树 15/19；缺 快速喷火船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：火炮术（炮塔/手推炮/炮舰射程+2）</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4863,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -4770,12 +4878,12 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>火炮术（炮塔/手推炮/炮舰射程+2）</t>
+          <t>弩箭匣（弓兵系/战车/楼船可发更多弩箭）；攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；海军科技树 15/19；缺 快速喷火船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：火炮术（炮塔/手推炮/炮舰射程+2）</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
         </is>
       </c>
     </row>
@@ -4785,7 +4893,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -4800,12 +4908,12 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>TC/码头生命+100%，黑暗/封建/城堡/帝王工作速度+5/10/15/20%</t>
+          <t>箭船系攻速+25%；运输船生命+100%，运载+20</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；海军科技树 15/19；缺 德罗蒙战舰、造船匠、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：TC/码头生命+100%，黑暗/封建/城堡/帝王工作速度+5/10/15/20%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 14/19；缺 快速喷火船、德罗蒙战舰、造船匠、精锐卡拉维尔战舰；最直接一条：箭船系攻速+25%</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4923,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -4830,22 +4938,22 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>攻城武器/攻城战舰城堡/帝王移速+10/15%；弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
+          <t>炮舰攻击移动目标更准</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：炮舰攻击移动目标更准</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="51" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -4860,22 +4968,22 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>箭船系攻速+25%；运输船生命+100%，运载+20</t>
+          <t>火矛兵/喷火船城堡/帝王移速+5/10%；火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；海军科技树 14/19；缺 快速喷火船、德罗蒙战舰、造船匠、精锐卡拉维尔战舰；最直接一条：箭船系攻速+25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：火矛兵/喷火船城堡/帝王移速+5/10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="51" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -4890,22 +4998,22 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>炮舰攻击移动目标更准</t>
+          <t>希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）；伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：炮舰攻击移动目标更准</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 0）；海军科技树 3/19；缺 大型战舰、快速喷火船、喷火船、喷火船；最直接一条：希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="51" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -4920,22 +5028,22 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>火矛兵/喷火船城堡/帝王移速+5/10%；火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
+          <t>维京长船/大型投石战舰生命+20%</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：火矛兵/喷火船城堡/帝王移速+5/10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="66" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；海军科技树 12/19；缺 快速喷火船、重型爆破船、精锐炮舰、炮舰；最直接一条：维京长船/大型投石战舰生命+20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="51" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -4950,22 +5058,22 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>村民/捕鱼船存食+10%；希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）；伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
+          <t>霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 0）；海军科技树 3/19；缺 大型战舰、快速喷火船、喷火船、喷火船；最直接一条：希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；海军科技树 11/19；缺 快速喷火船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="51" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -4980,22 +5088,22 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>维京长船/大型投石战舰生命+20%</t>
+          <t>芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；海军科技树 12/19；缺 快速喷火船、重型爆破船、精锐炮舰、炮舰；最直接一条：维京长船/大型投石战舰生命+20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 4/19；缺 大型战舰、快速喷火船、喷火船、喷火船；最直接一条：芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -5010,12 +5118,12 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
+          <t>船舰封建/城堡/帝王生命+10/15/20%；环球探险（地图全待探索；船只训练+33%）</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；海军科技树 11/19；缺 快速喷火船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 1）；海军科技树 15/19；缺 快速喷火船、重型爆破船、德罗蒙战舰、造船匠</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5133,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -5040,12 +5148,12 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>牵引抛石机/楼船费用-25%</t>
+          <t>船舰移速+10%</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；海军科技树 11/19；缺 重型爆破船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：牵引抛石机/楼船费用-25%</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
         </is>
       </c>
     </row>
@@ -5055,7 +5163,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -5070,22 +5178,22 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>造船厂工作速度+15%；芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
+          <t>船舰每分钟回15生命</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；海军科技树 4/19；缺 大型战舰、快速喷火船、喷火船、喷火船；最直接一条：芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="51" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -5100,12 +5208,12 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>船舰封建/城堡/帝王生命+10/15/20%；环球探险（地图全待探索；船只训练+33%）</t>
+          <t>牵引抛石机/楼船费用-25%</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 0）；海军科技树 15/19；缺 快速喷火船、重型爆破船、德罗蒙战舰、造船匠</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；海军科技树 11/19；缺 重型爆破船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：牵引抛石机/楼船费用-25%</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5223,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -5130,22 +5238,22 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>船舰移速+10%</t>
+          <t>运输船视野 +5 且费用 -50%</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="36" customHeight="1">
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；海军科技树 15/19；缺 精锐炮舰、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="51" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -5160,22 +5268,22 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>船舰每分钟回15生命</t>
+          <t>渔夫/捕鱼船携带+15；码头提供的人口空间 +5</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="36" customHeight="1">
+          <t>阶段3·资源效率；原生条目 4 条（强 2 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：渔夫/捕鱼船携带+15</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="51" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -5190,12 +5298,12 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>运输船视野 +5 且费用 -50%</t>
+          <t>TC/码头生命+100%，黑暗/封建/城堡/帝王工作速度+5/10/15/20%</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；海军科技树 15/19；缺 精锐炮舰、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
+          <t>阶段3·资源效率；原生条目 2 条（强 1 / 弱 0）；海军科技树 15/19；缺 德罗蒙战舰、造船匠、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：TC/码头生命+100%，黑暗/封建/城堡/帝王工作速度+5/10/15/20%</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5333,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；海军科技树 3/19；缺 大型战舰、快速喷火船、喷火船、喷火船</t>
+          <t>阶段3·资源效率；原生条目 1 条（强 0 / 弱 0）；海军科技树 3/19；缺 大型战舰、快速喷火船、喷火船、喷火船</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6351,101 +6459,141 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>① 只看直接作用于海军本体、或其前置/费用/产出的条目；</t>
+          <t>本表按用户打法口径分四个阶段排序：先加强要玩的主流派兵种，再减它的资源消耗，最后才补资源效率。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="12" t="inlineStr"/>
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>① 阶段 1 · 本体强化</t>
+        </is>
+      </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>② 泛用条目与兵种类一律剔除（放进「与海战流无关·可跳过」）；</t>
+          <t>直接加强海军本体的条目（攻击/护甲/生命/攻速/射程/移速/回血/数量/生产训练速度/解锁升级等）。这一档最优先。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="12" t="inlineStr"/>
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>② 阶段 2 · 减费用</t>
+        </is>
+      </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>③ 门槛越低、替代成本越高，名次越靠前。</t>
+          <t>降低该兵种及同系兵种（船坞单位）生产所需资源的条目：费用/成本 -N%、升级免费、用其它资源替代。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="12" t="inlineStr"/>
-      <c r="B15" s="12" t="inlineStr"/>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>③ 阶段 3 · 资源效率</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>采集/产出/携带/贸易/人口/经济科技等让主流派更快成型的条目。</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>未验证项</t>
+          <t>④ 阶段 4 · 其他相关</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
+          <t>其余与本流派相关、但不属于上述三类的条目。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>★ 最重要的一条：别买重复</t>
-        </is>
-      </c>
+      <c r="A17" s="12" t="inlineStr"/>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
+          <t>同阶段内按「人工权威顺序（实战强度）」再排；泛用条目与兵种类一律剔除（放进「与海战流无关·可跳过」）。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="12" t="inlineStr"/>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
-        </is>
-      </c>
+      <c r="B18" s="12" t="inlineStr"/>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>数据来源</t>
+          <t>未验证项</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+          <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="12" t="inlineStr"/>
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>★ 最重要的一条：别买重复</t>
+        </is>
+      </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>整理</t>
-        </is>
-      </c>
+      <c r="A21" s="12" t="inlineStr"/>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>By RemonBo；本表由 DSH 生成。</t>
+          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
         <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="12" t="inlineStr"/>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>整理</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>By RemonBo；本表由 DSH 生成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
           <t>与本表配套</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>同目录下的箭塔流、炮塔流与其余流派总表。</t>
         </is>

--- a/帝国时代2决定版 文明联盟 海战流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 海战流最优研究顺序 By RemonBo.xlsx
@@ -20,9 +20,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·海军本体强化'!$A$1:$E$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·海军本体强化'!$A$1:$E$47</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·海军本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与海战流无关·可跳过'!$A$1:$D$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与海战流无关·可跳过'!$1:$1</definedName>
@@ -587,7 +587,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>军事建筑/码头建成后食物+55；赤壁战术（爆破船/火焰弓箭手对船只/建筑火焰伤害）；卧虎（牵引抛石机/楼船巨型投石武器发更多弹药）</t>
+          <t>赤壁战术（爆破船/火焰弓箭手对船只/建筑火焰伤害）；卧虎（牵引抛石机/楼船巨型投石武器发更多弹药）；军事建筑/码头建成后食物+55</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -610,17 +610,17 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="51" customHeight="1">
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>马来（备选）</t>
+          <t>达罗毗荼（备选）</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：海上霸主（码头升级为巨港）</t>
+          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：渔夫/捕鱼船携带+15</t>
         </is>
       </c>
     </row>
@@ -656,13 +656,13 @@
       <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>高丽（备选）</t>
+          <t>马来（备选）</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：战船木材-20%</t>
+          <t>备选：阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：海上霸主（码头升级为巨港）</t>
         </is>
       </c>
     </row>
@@ -670,13 +670,13 @@
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>罗马（备选）</t>
+          <t>高丽（备选）</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 13/19；缺 重型爆破船、精锐炮舰、炮舰、干船坞；最直接一条：箭船系/德罗蒙战舰近战护甲+1/远程护甲+1</t>
+          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：战船木材-20%</t>
         </is>
       </c>
     </row>
@@ -708,31 +708,31 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1">
+    <row r="11" ht="51" customHeight="1">
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚（备选）</t>
+          <t>罗马（备选）</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、造船匠；最直接一条：箭船系/德罗蒙战舰可多发一炮弹</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="51" customHeight="1">
+          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 13/19；缺 重型爆破船、精锐炮舰、炮舰、干船坞；最直接一条：箭船系/德罗蒙战舰近战护甲+1/远程护甲+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>日本（备选）</t>
+          <t>亚美尼亚（备选）</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：箭船系视野 +4</t>
+          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、造船匠；最直接一条：箭船系/德罗蒙战舰可多发一炮弹</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>三列桨手制（单列桨座战船系冲锋造成额外范围伤害且充能更快）；提洛同盟（港口/造船厂附近战船攻速+15%）；TC可切换政策风格（经济/海军/军事）</t>
+          <t>三列桨手制（单列桨座战船系冲锋造成额外范围伤害且充能更快）；提洛同盟（港口/造船厂附近战船攻速+15%）；造船厂科技研究速度 +50%</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>海上霸主（码头升级为巨港）；码头视野 +6；养鱼场费用-33%且食物+200%</t>
+          <t>渔夫/捕鱼船携带+15；码头提供的人口空间 +5</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：海上霸主（码头升级为巨港）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：渔夫/捕鱼船携带+15</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>战船木材-20%；神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）</t>
+          <t>海上霸主（码头升级为巨港）；码头视野 +6</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：战船木材-20%</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：海上霸主（码头升级为巨港）</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>箭船系/德罗蒙战舰近战护甲+1/远程护甲+1；弩炮（蝎式弩攻速+33%；箭船系攻+2）</t>
+          <t>神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 13/19；缺 重型爆破船、精锐炮舰、炮舰、干船坞；最直接一条：箭船系/德罗蒙战舰近战护甲+1/远程护甲+1</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：战船木材-20%</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>箭船系/德罗蒙战舰可多发一炮弹；奇里乞亚舰队（爆破船爆炸范围+20%；箭船系/德罗蒙战舰射程+1）</t>
+          <t>箭船系/德罗蒙战舰近战护甲+1/远程护甲+1；弩炮（蝎式弩攻速+33%；箭船系攻+2）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、造船匠；最直接一条：箭船系/德罗蒙战舰可多发一炮弹</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 13/19；缺 重型爆破船、精锐炮舰、炮舰、干船坞；最直接一条：箭船系/德罗蒙战舰近战护甲+1/远程护甲+1</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -963,17 +963,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>箭船系视野 +4；捕鱼船黑暗/封建/城堡/帝王工作+5/10/15/20%，生命+100%</t>
+          <t>箭船系/德罗蒙战舰可多发一炮弹；奇里乞亚舰队（爆破船爆炸范围+20%；箭船系/德罗蒙战舰射程+1）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>黑暗时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：箭船系视野 +4</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、造船匠；最直接一条：箭船系/德罗蒙战舰可多发一炮弹</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>码头/大学科技-25%；捕鱼船-15%</t>
+          <t>箭船系视野 +4；捕鱼船黑暗/封建/城堡/帝王工作+5/10/15/20%，生命+100%</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>黑暗时代起</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：码头/大学科技-25%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：箭船系视野 +4</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>瓦兰吉/维京长船移速+10%；北方人之怒（投石车系/大型投石战舰射程+1；攻城武器/攻城战舰对建筑攻+40%）</t>
+          <t>瓦兰吉/维京长船移速+10%；捕鱼船/村民存食+5%；北方人之怒（投石车系/大型投石战舰射程+1；攻城武器/攻城战舰对建筑攻+40%）</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>弩箭匣（弓兵系/战车/楼船可发更多弩箭）；攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
+          <t>TC/码头生命+100%，黑暗/封建/城堡/帝王工作速度+5/10/15/20%</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>黑暗时代起</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；海军科技树 15/19；缺 德罗蒙战舰、造船匠、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：TC/码头生命+100%，黑暗/封建/城堡/帝王工作速度+5/10/15/20%</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1143,17 +1143,17 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>箭船系攻速+25%；运输船生命+100%，运载+20</t>
+          <t>弩箭匣（弓兵系/战车/楼船可发更多弩箭）；攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 14/19；缺 快速喷火船、德罗蒙战舰、造船匠、精锐卡拉维尔战舰；最直接一条：箭船系攻速+25%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>炮舰攻击移动目标更准</t>
+          <t>箭船系攻速+25%；运输船生命+100%，运载+20</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：炮舰攻击移动目标更准</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 14/19；缺 快速喷火船、德罗蒙战舰、造船匠、精锐卡拉维尔战舰；最直接一条：箭船系攻速+25%</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1203,17 +1203,17 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>火矛兵/喷火船城堡/帝王移速+5/10%；火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
+          <t>炮舰攻击移动目标更准</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：火矛兵/喷火船城堡/帝王移速+5/10%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：炮舰攻击移动目标更准</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1233,27 +1233,27 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）；伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
+          <t>火矛兵/喷火船城堡/帝王移速+5/10%；火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 0）；海军科技树 3/19；缺 大型战舰、快速喷火船、喷火船、喷火船；最直接一条：希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：火矛兵/喷火船城堡/帝王移速+5/10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="66" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>维京长船/大型投石战舰生命+20%</t>
+          <t>希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）；伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）；村民/捕鱼船存食+10%</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；海军科技树 12/19；缺 快速喷火船、重型爆破船、精锐炮舰、炮舰；最直接一条：维京长船/大型投石战舰生命+20%</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 0）；海军科技树 3/19；缺 大型战舰、快速喷火船、喷火船、喷火船；最直接一条：希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
+          <t>芦苇箭（弓兵/远程长生军/箭船攻速+25%）；造船厂工作速度+15%</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；海军科技树 11/19；缺 快速喷火船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 4/19；缺 大型战舰、快速喷火船、喷火船、喷火船；最直接一条：芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
+          <t>维京长船/大型投石战舰生命+20%</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1333,17 +1333,17 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 4/19；缺 大型战舰、快速喷火船、喷火船、喷火船；最直接一条：芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；海军科技树 12/19；缺 快速喷火船、重型爆破船、精锐炮舰、炮舰；最直接一条：维京长船/大型投石战舰生命+20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="51" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1353,17 +1353,17 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>船舰封建/城堡/帝王生命+10/15/20%；环球探险（地图全待探索；船只训练+33%）</t>
+          <t>霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>封建时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 1）；海军科技树 15/19；缺 快速喷火船、重型爆破船、德罗蒙战舰、造船匠</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；海军科技树 11/19；缺 快速喷火船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>船舰移速+10%</t>
+          <t>村民/捕鱼船采牡蛎+15%</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；海军科技树 3/19；缺 大型战舰、快速喷火船、喷火船、喷火船</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1413,27 +1413,27 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>船舰每分钟回15生命</t>
+          <t>船舰封建/城堡/帝王生命+10/15/20%；环球探险（地图全待探索；船只训练+33%）</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>封建时代起</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 1）；海军科技树 15/19；缺 快速喷火船、重型爆破船、德罗蒙战舰、造船匠</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>牵引抛石机/楼船费用-25%</t>
+          <t>船舰移速+10%</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；海军科技树 11/19；缺 重型爆破船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：牵引抛石机/楼船费用-25%</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>运输船视野 +5 且费用 -50%</t>
+          <t>船舰每分钟回15生命</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；海军科技树 15/19；缺 精锐炮舰、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>渔夫/捕鱼船携带+15；码头提供的人口空间 +5</t>
+          <t>码头/大学科技-25%；捕鱼船-15%</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>阶段3·资源效率；原生条目 4 条（强 2 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：渔夫/捕鱼船携带+15</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="51" customHeight="1">
+          <t>阶段2·减费用；原生条目 3 条（强 1 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：码头/大学科技-25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1533,27 +1533,27 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>TC/码头生命+100%，黑暗/封建/城堡/帝王工作速度+5/10/15/20%</t>
+          <t>运输船视野 +5 且费用 -50%</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>黑暗时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>阶段3·资源效率；原生条目 2 条（强 1 / 弱 0）；海军科技树 15/19；缺 德罗蒙战舰、造船匠、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：TC/码头生命+100%，黑暗/封建/城堡/帝王工作速度+5/10/15/20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="36" customHeight="1">
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；海军科技树 15/19；缺 精锐炮舰、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="51" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>村民/捕鱼船采牡蛎+15%</t>
+          <t>牵引抛石机/楼船费用-25%</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>阶段3·资源效率；原生条目 1 条（强 0 / 弱 0）；海军科技树 3/19；缺 大型战舰、快速喷火船、喷火船、喷火船</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；海军科技树 11/19；缺 重型爆破船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：牵引抛石机/楼船费用-25%</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1716,22 +1716,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>修船厂/干船坞免费</t>
+          <t>博格斯维加尔（弓兵系/维京长船攻+1）</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>免费获得，等于直接省下这笔支出</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -1743,22 +1743,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>博格斯维加尔（弓兵系/维京长船攻+1）</t>
+          <t>喷火/德罗蒙攻速+25%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
@@ -1775,34 +1775,34 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>喷火/德罗蒙攻速+25%</t>
+          <t>希腊之火（喷火船射程+1；德罗蒙和炮塔爆炸范围提升）</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>攻速提升，直接抬高输出</t>
+          <t>爆炸/溅射范围提升</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>希腊之火（喷火船射程+1；德罗蒙和炮塔爆炸范围提升）</t>
+          <t>三列桨手制（单列桨座战船系冲锋造成额外范围伤害且充能更快）</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>爆炸/溅射范围提升</t>
+          <t>附加范围/冲击伤害，团战更占优</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>三列桨手制（单列桨座战船系冲锋造成额外范围伤害且充能更快）</t>
+          <t>提洛同盟（港口/造船厂附近战船攻速+15%）</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>附加范围/冲击伤害，团战更占优</t>
+          <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
@@ -1856,17 +1856,17 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>提洛同盟（港口/造船厂附近战船攻速+15%）</t>
+          <t>造船厂科技研究速度 +50%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>攻速提升，直接抬高输出</t>
+          <t>研究/生产速度提升，科技与产能来得更快</t>
         </is>
       </c>
     </row>
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>雅典</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>TC可切换政策风格（经济/海军/军事）</t>
+          <t>渔夫/捕鱼船携带+15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1893,11 +1893,11 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>可切换政策风格，按局势临时调整</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>A</t>
@@ -1905,12 +1905,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>雅典</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>造船厂科技研究速度 +50%</t>
+          <t>码头提供的人口空间 +5</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>研究/生产速度提升，科技与产能来得更快</t>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
         </is>
       </c>
     </row>
@@ -1986,22 +1986,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>养鱼场费用-33%且食物+200%</t>
+          <t>神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>射程提升</t>
         </is>
       </c>
     </row>
@@ -2013,12 +2013,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>战船木材-20%</t>
+          <t>箭船系/德罗蒙战舰近战护甲+1/远程护甲+1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -2040,12 +2040,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）</t>
+          <t>弩炮（蝎式弩攻速+33%；箭船系攻+2）</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2055,24 +2055,24 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>射程提升</t>
+          <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>箭船系/德罗蒙战舰近战护甲+1/远程护甲+1</t>
+          <t>箭船系/德罗蒙战舰可多发一炮弹</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2082,24 +2082,24 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>弩炮（蝎式弩攻速+33%；箭船系攻+2）</t>
+          <t>奇里乞亚舰队（爆破船爆炸范围+20%；箭船系/德罗蒙战舰射程+1）</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2109,61 +2109,61 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>攻速提升，直接抬高输出</t>
+          <t>爆炸/溅射范围提升</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>箭船系/德罗蒙战舰可多发一炮弹</t>
+          <t>箭船系视野 +4</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>视野提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>捕鱼船黑暗/封建/城堡/帝王工作+5/10/15/20%，生命+100%</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>亚美尼亚</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>奇里乞亚舰队（爆破船爆炸范围+20%；箭船系/德罗蒙战舰射程+1）</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>爆炸/溅射范围提升</t>
+          <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
@@ -2175,22 +2175,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>箭船系视野 +4</t>
+          <t>瓦兰吉/维京长船移速+10%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>视野提升</t>
+          <t>机动性提升</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>捕鱼船黑暗/封建/城堡/帝王工作+5/10/15/20%，生命+100%</t>
+          <t>捕鱼船/村民存食+5%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2217,11 +2217,11 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
+          <t>资源存放上限提升，少跑几趟</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
           <t>B</t>
@@ -2229,22 +2229,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>码头/大学科技-25%</t>
+          <t>北方人之怒（投石车系/大型投石战舰射程+1；攻城武器/攻城战舰对建筑攻+40%）</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>射程提升</t>
         </is>
       </c>
     </row>
@@ -2256,12 +2256,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>捕鱼船-15%</t>
+          <t>维京长船/大型投石战舰攻速+15%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>瓦兰吉/维京长船移速+10%</t>
+          <t>牧羊/捕鱼/狩猎也产黄金</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2298,11 +2298,11 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>机动性提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="36" customHeight="1">
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
           <t>B</t>
@@ -2310,12 +2310,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>北方人之怒（投石车系/大型投石战舰射程+1；攻城武器/攻城战舰对建筑攻+40%）</t>
+          <t>火炮术（炮塔/手推炮/炮舰射程+2）</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>维京长船/大型投石战舰攻速+15%</t>
+          <t>TC/码头生命+100%，黑暗/封建/城堡/帝王工作速度+5/10/15/20%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>攻速提升，直接抬高输出</t>
+          <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
@@ -2364,22 +2364,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>牧羊/捕鱼/狩猎也产黄金</t>
+          <t>弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>采集效率提升，经济成型更快</t>
+          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
         </is>
       </c>
     </row>
@@ -2391,22 +2391,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>火炮术（炮塔/手推炮/炮舰射程+2）</t>
+          <t>攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>射程提升</t>
+          <t>机动性提升</t>
         </is>
       </c>
     </row>
@@ -2418,22 +2418,22 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
+          <t>箭船系攻速+25%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
+          <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
+          <t>运输船生命+100%，运载+20</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2460,11 +2460,11 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>机动性提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1">
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
           <t>B</t>
@@ -2472,12 +2472,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>箭船系攻速+25%</t>
+          <t>炮舰攻击移动目标更准</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>攻速提升，直接抬高输出</t>
+          <t>提升命中率与对移动目标的准确度，减少空枪</t>
         </is>
       </c>
     </row>
@@ -2499,12 +2499,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>运输船生命+100%，运载+20</t>
+          <t>火矛兵/喷火船城堡/帝王移速+5/10%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2514,11 +2514,11 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="36" customHeight="1">
+          <t>机动性提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
           <t>B</t>
@@ -2526,130 +2526,130 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>炮舰攻击移动目标更准</t>
+          <t>火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>斯巴达</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>斯巴达</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>额外产出资源，经济滚雪球更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>斯巴达</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>村民/捕鱼船存食+10%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>提升命中率与对移动目标的准确度，减少空枪</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>中国</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>火矛兵/喷火船城堡/帝王移速+5/10%</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>机动性提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>中国</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>资源存放上限提升，少跑几趟</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>阿契美尼德</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升，正面更硬</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="36" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升，正面更硬</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>额外产出资源，经济滚雪球更快</t>
+          <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>维京长船/大型投石战舰生命+20%</t>
+          <t>造船厂工作速度+15%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>生命值提升，抗打更久</t>
+          <t>工作速度提升，成型更快</t>
         </is>
       </c>
     </row>
@@ -2688,22 +2688,22 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
+          <t>维京长船/大型投石战舰生命+20%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>爆炸/溅射范围提升</t>
+          <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
@@ -2715,12 +2715,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
+          <t>霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>攻速提升，直接抬高输出</t>
+          <t>爆炸/溅射范围提升</t>
         </is>
       </c>
     </row>
@@ -2742,12 +2742,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>船舰封建/城堡/帝王生命+10/15/20%</t>
+          <t>村民/捕鱼船采牡蛎+15%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>生命值提升，抗打更久</t>
+          <t>采集效率提升，经济成型更快</t>
         </is>
       </c>
     </row>
@@ -2774,17 +2774,17 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>环球探险（地图全待探索；船只训练+33%）</t>
+          <t>船舰封建/城堡/帝王生命+10/15/20%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>训练速度提升，成型更快</t>
+          <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
@@ -2796,22 +2796,22 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>船舰移速+10%</t>
+          <t>环球探险（地图全待探索；船只训练+33%）</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>机动性提升</t>
+          <t>训练速度提升，成型更快</t>
         </is>
       </c>
     </row>
@@ -2823,27 +2823,54 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>船舰移速+10%</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>机动性提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>孟加拉</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>船舰每分钟回15生命</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>持续回血，长期更省维修成本</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E46"/>
+  <autoFilter ref="A1:E47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2855,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2900,12 +2927,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>战船封建/城堡/帝王费用-10/15/20%</t>
+          <t>修船厂/干船坞免费</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2915,7 +2942,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>免费获得，等于直接省下这笔支出</t>
         </is>
       </c>
     </row>
@@ -2932,71 +2959,71 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
+          <t>战船封建/城堡/帝王费用-10/15/20%</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>维京</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
           <t>码头费用 -15%</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>丹麦人</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>捕鱼船/村民存食+5%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>高丽</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>战船木材-20%</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>资源存放上限提升，少跑几趟</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>村民/捕鱼船存食+10%</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>资源存放上限提升，少跑几趟</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3035,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>造船厂工作速度+15%</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -3023,7 +3050,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>工作速度提升，成型更快</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
@@ -3035,12 +3062,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>所有单位黄金费用-20%</t>
+          <t>码头/大学科技-25%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -3062,12 +3089,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>牵引抛石机/楼船费用-25%</t>
+          <t>捕鱼船-15%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -3116,12 +3143,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>渔夫/捕鱼船携带+15</t>
+          <t>牵引抛石机/楼船费用-25%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3131,93 +3158,12 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>达罗毗荼</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>码头提供的人口空间 +5</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>波斯</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>TC/码头生命+100%，黑暗/封建/城堡/帝王工作速度+5/10/15/20%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>普鲁人</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>村民/捕鱼船采牡蛎+15%</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E13"/>
+  <autoFilter ref="A1:E10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -4142,22 +4088,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>海上霸主（码头升级为巨港）；码头视野 +6</t>
+          <t>渔夫/捕鱼船携带+15；码头提供的人口空间 +5</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2）；海军科技树 15/19。缺：重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
+          <t>原生条目 2 条（强 2）；海军科技树 16/19。缺：德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4113,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -4177,12 +4123,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>战船木材-20%；神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）</t>
+          <t>海上霸主（码头升级为巨港）；码头视野 +6</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；海军科技树 15/19。缺：重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
+          <t>原生条目 3 条（强 2）；海军科技树 15/19。缺：重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
         </is>
       </c>
     </row>
@@ -4192,22 +4138,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>15/19</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>箭船系/德罗蒙战舰近战护甲+1/远程护甲+1；弩炮（蝎式弩攻速+33%；箭船系攻+2）</t>
+          <t>战船木材-20%；神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；海军科技树 13/19。缺：重型爆破船、精锐炮舰、炮舰、干船坞、精锐卡拉维尔战舰</t>
+          <t>原生条目 2 条（强 2）；海军科技树 15/19。缺：重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4163,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -4227,12 +4173,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>箭船系/德罗蒙战舰可多发一炮弹；奇里乞亚舰队（爆破船爆炸范围+20%；箭船系/德罗蒙战舰射程+1）</t>
+          <t>箭船系/德罗蒙战舰近战护甲+1/远程护甲+1；弩炮（蝎式弩攻速+33%；箭船系攻+2）</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；海军科技树 13/19。缺：快速喷火船、精锐炮舰、炮舰、造船匠、精锐卡拉维尔战舰</t>
+          <t>原生条目 2 条（强 2）；海军科技树 13/19。缺：重型爆破船、精锐炮舰、炮舰、干船坞、精锐卡拉维尔战舰</t>
         </is>
       </c>
     </row>
@@ -4242,22 +4188,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>13/19</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>箭船系视野 +4</t>
+          <t>箭船系/德罗蒙战舰可多发一炮弹；奇里乞亚舰队（爆破船爆炸范围+20%；箭船系/德罗蒙战舰射程+1）</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1）；海军科技树 15/19。缺：重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
+          <t>原生条目 2 条（强 2）；海军科技树 13/19。缺：快速喷火船、精锐炮舰、炮舰、造船匠、精锐卡拉维尔战舰</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4213,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -4277,7 +4223,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>码头/大学科技-25%</t>
+          <t>箭船系视野 +4</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -4367,22 +4313,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>15/19</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
+          <t>TC/码头生命+100%，黑暗/封建/城堡/帝王工作速度+5/10/15/20%</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1）；海军科技树 13/19。缺：快速喷火船、精锐炮舰、炮舰、德罗蒙战舰、精锐卡拉维尔战舰</t>
+          <t>原生条目 1 条（强 1）；海军科技树 15/19。缺：德罗蒙战舰、造船匠、精锐卡拉维尔战舰、卡拉维尔战舰</t>
         </is>
       </c>
     </row>
@@ -4392,22 +4338,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>13/19</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>箭船系攻速+25%</t>
+          <t>弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1）；海军科技树 14/19。缺：快速喷火船、德罗蒙战舰、造船匠、精锐卡拉维尔战舰、卡拉维尔战舰</t>
+          <t>原生条目 2 条（强 1）；海军科技树 13/19。缺：快速喷火船、精锐炮舰、炮舰、德罗蒙战舰、精锐卡拉维尔战舰</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4434,7 @@
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>军事建筑/码头建成后食物+55；赤壁战术（爆破船/火焰弓箭手对船只/建筑火焰伤害）；卧虎（牵引抛石机/楼船巨型投石武器发更多弹药）</t>
+          <t>赤壁战术（爆破船/火焰弓箭手对船只/建筑火焰伤害）；卧虎（牵引抛石机/楼船巨型投石武器发更多弹药）；军事建筑/码头建成后食物+55</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -4578,7 +4524,7 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>三列桨手制（单列桨座战船系冲锋造成额外范围伤害且充能更快）；提洛同盟（港口/造船厂附近战船攻速+15%）；TC可切换政策风格（经济/海军/军事）</t>
+          <t>三列桨手制（单列桨座战船系冲锋造成额外范围伤害且充能更快）；提洛同盟（港口/造船厂附近战船攻速+15%）；造船厂科技研究速度 +50%</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -4593,7 +4539,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -4608,12 +4554,12 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>海上霸主（码头升级为巨港）；码头视野 +6；养鱼场费用-33%且食物+200%</t>
+          <t>渔夫/捕鱼船携带+15；码头提供的人口空间 +5</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：海上霸主（码头升级为巨港）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：渔夫/捕鱼船携带+15</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4569,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -4638,12 +4584,12 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>战船木材-20%；神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）</t>
+          <t>海上霸主（码头升级为巨港）；码头视野 +6</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：战船木材-20%</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：海上霸主（码头升级为巨港）</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4599,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -4668,12 +4614,12 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>箭船系/德罗蒙战舰近战护甲+1/远程护甲+1；弩炮（蝎式弩攻速+33%；箭船系攻+2）</t>
+          <t>神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 13/19；缺 重型爆破船、精锐炮舰、炮舰、干船坞；最直接一条：箭船系/德罗蒙战舰近战护甲+1/远程护甲+1</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：战船木材-20%</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4629,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4698,12 +4644,12 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>箭船系/德罗蒙战舰可多发一炮弹；奇里乞亚舰队（爆破船爆炸范围+20%；箭船系/德罗蒙战舰射程+1）</t>
+          <t>箭船系/德罗蒙战舰近战护甲+1/远程护甲+1；弩炮（蝎式弩攻速+33%；箭船系攻+2）</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、造船匠；最直接一条：箭船系/德罗蒙战舰可多发一炮弹</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 13/19；缺 重型爆破船、精锐炮舰、炮舰、干船坞；最直接一条：箭船系/德罗蒙战舰近战护甲+1/远程护甲+1</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4659,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -4728,12 +4674,12 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>箭船系视野 +4；捕鱼船黑暗/封建/城堡/帝王工作+5/10/15/20%，生命+100%</t>
+          <t>箭船系/德罗蒙战舰可多发一炮弹；奇里乞亚舰队（爆破船爆炸范围+20%；箭船系/德罗蒙战舰射程+1）</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：箭船系视野 +4</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、造船匠；最直接一条：箭船系/德罗蒙战舰可多发一炮弹</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4689,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -4758,12 +4704,12 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>码头/大学科技-25%；捕鱼船-15%</t>
+          <t>箭船系视野 +4；捕鱼船黑暗/封建/城堡/帝王工作+5/10/15/20%，生命+100%</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：码头/大学科技-25%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：箭船系视野 +4</t>
         </is>
       </c>
     </row>
@@ -4788,7 +4734,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>瓦兰吉/维京长船移速+10%；北方人之怒（投石车系/大型投石战舰射程+1；攻城武器/攻城战舰对建筑攻+40%）</t>
+          <t>瓦兰吉/维京长船移速+10%；捕鱼船/村民存食+5%；北方人之怒（投石车系/大型投石战舰射程+1；攻城武器/攻城战舰对建筑攻+40%）</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -4863,7 +4809,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -4878,12 +4824,12 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>弩箭匣（弓兵系/战车/楼船可发更多弩箭）；攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
+          <t>TC/码头生命+100%，黑暗/封建/城堡/帝王工作速度+5/10/15/20%</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；海军科技树 15/19；缺 德罗蒙战舰、造船匠、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：TC/码头生命+100%，黑暗/封建/城堡/帝王工作速度+5/10/15/20%</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4839,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -4908,12 +4854,12 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>箭船系攻速+25%；运输船生命+100%，运载+20</t>
+          <t>弩箭匣（弓兵系/战车/楼船可发更多弩箭）；攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 14/19；缺 快速喷火船、德罗蒙战舰、造船匠、精锐卡拉维尔战舰；最直接一条：箭船系攻速+25%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4869,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -4938,12 +4884,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>炮舰攻击移动目标更准</t>
+          <t>箭船系攻速+25%；运输船生命+100%，运载+20</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：炮舰攻击移动目标更准</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 14/19；缺 快速喷火船、德罗蒙战舰、造船匠、精锐卡拉维尔战舰；最直接一条：箭船系攻速+25%</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4899,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -4968,12 +4914,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>火矛兵/喷火船城堡/帝王移速+5/10%；火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
+          <t>炮舰攻击移动目标更准</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：火矛兵/喷火船城堡/帝王移速+5/10%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：炮舰攻击移动目标更准</t>
         </is>
       </c>
     </row>
@@ -4983,7 +4929,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -4998,22 +4944,22 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）；伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
+          <t>火矛兵/喷火船城堡/帝王移速+5/10%；火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 0）；海军科技树 3/19；缺 大型战舰、快速喷火船、喷火船、喷火船；最直接一条：希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；海军科技树 13/19；缺 快速喷火船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：火矛兵/喷火船城堡/帝王移速+5/10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -5028,12 +4974,12 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>维京长船/大型投石战舰生命+20%</t>
+          <t>希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）；伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）；村民/捕鱼船存食+10%</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；海军科技树 12/19；缺 快速喷火船、重型爆破船、精锐炮舰、炮舰；最直接一条：维京长船/大型投石战舰生命+20%</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 0）；海军科技树 3/19；缺 大型战舰、快速喷火船、喷火船、喷火船；最直接一条：希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）</t>
         </is>
       </c>
     </row>
@@ -5043,7 +4989,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -5058,12 +5004,12 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
+          <t>芦苇箭（弓兵/远程长生军/箭船攻速+25%）；造船厂工作速度+15%</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；海军科技树 11/19；缺 快速喷火船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 4/19；缺 大型战舰、快速喷火船、喷火船、喷火船；最直接一条：芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
         </is>
       </c>
     </row>
@@ -5073,7 +5019,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -5088,22 +5034,22 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
+          <t>维京长船/大型投石战舰生命+20%</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；海军科技树 4/19；缺 大型战舰、快速喷火船、喷火船、喷火船；最直接一条：芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；海军科技树 12/19；缺 快速喷火船、重型爆破船、精锐炮舰、炮舰；最直接一条：维京长船/大型投石战舰生命+20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="51" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -5118,12 +5064,12 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>船舰封建/城堡/帝王生命+10/15/20%；环球探险（地图全待探索；船只训练+33%）</t>
+          <t>霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 1）；海军科技树 15/19；缺 快速喷火船、重型爆破船、德罗蒙战舰、造船匠</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；海军科技树 11/19；缺 快速喷火船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5079,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -5148,12 +5094,12 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>船舰移速+10%</t>
+          <t>村民/捕鱼船采牡蛎+15%</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；海军科技树 3/19；缺 大型战舰、快速喷火船、喷火船、喷火船</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5109,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -5178,22 +5124,22 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>船舰每分钟回15生命</t>
+          <t>船舰封建/城堡/帝王生命+10/15/20%；环球探险（地图全待探索；船只训练+33%）</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 1）；海军科技树 15/19；缺 快速喷火船、重型爆破船、德罗蒙战舰、造船匠</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -5208,12 +5154,12 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>牵引抛石机/楼船费用-25%</t>
+          <t>船舰移速+10%</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；海军科技树 11/19；缺 重型爆破船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：牵引抛石机/楼船费用-25%</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5169,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -5238,12 +5184,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>运输船视野 +5 且费用 -50%</t>
+          <t>船舰每分钟回15生命</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；海军科技树 15/19；缺 精锐炮舰、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5199,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -5268,22 +5214,22 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>渔夫/捕鱼船携带+15；码头提供的人口空间 +5</t>
+          <t>码头/大学科技-25%；捕鱼船-15%</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>阶段3·资源效率；原生条目 4 条（强 2 / 弱 0）；海军科技树 16/19；缺 德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：渔夫/捕鱼船携带+15</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="51" customHeight="1">
+          <t>阶段2·减费用；原生条目 3 条（强 1 / 弱 0）；海军科技树 15/19；缺 重型爆破船、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：码头/大学科技-25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -5298,22 +5244,22 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>TC/码头生命+100%，黑暗/封建/城堡/帝王工作速度+5/10/15/20%</t>
+          <t>运输船视野 +5 且费用 -50%</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>阶段3·资源效率；原生条目 2 条（强 1 / 弱 0）；海军科技树 15/19；缺 德罗蒙战舰、造船匠、精锐卡拉维尔战舰、卡拉维尔战舰；最直接一条：TC/码头生命+100%，黑暗/封建/城堡/帝王工作速度+5/10/15/20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="36" customHeight="1">
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；海军科技树 15/19；缺 精锐炮舰、德罗蒙战舰、精锐卡拉维尔战舰、卡拉维尔战舰</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="51" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -5328,12 +5274,12 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>村民/捕鱼船采牡蛎+15%</t>
+          <t>牵引抛石机/楼船费用-25%</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>阶段3·资源效率；原生条目 1 条（强 0 / 弱 0）；海军科技树 3/19；缺 大型战舰、快速喷火船、喷火船、喷火船</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；海军科技树 11/19；缺 重型爆破船、精锐炮舰、炮舰、德罗蒙战舰；最直接一条：牵引抛石机/楼船费用-25%</t>
         </is>
       </c>
     </row>
